--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,240 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/08 14:59:13</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5952.38</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/08 19:26:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5664</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/08 14:59:19</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.38</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/16 21:57:29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27710.84</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>230000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27710.84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27710.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,186 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/16 21:57:29</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>230000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>27710.84</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27710.84</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27710.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/17 14:56:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8139.53</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8139.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/17 16:38:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8139.53</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7139.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/17 16:38:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/17 16:38:01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8139</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7139.53</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,240 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/17 14:56:30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8139.53</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 16:38:54</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7139</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 16:38:01</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8139.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8139</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.53</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/20 11:33:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8139.53</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8139.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/20 12:18:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8139.53</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7139.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/20 12:45:32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/20 12:18:03</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8139.53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8139</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7139.53</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -75,237 +75,279 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/20 17:33:22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5882.35</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/20 11:33:30</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>8139.53</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/20 12:45:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/20 12:18:03</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8139.53</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>14021.89</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8139</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.53</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5882.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/20 12:45:32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/20 12:18:03</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14021.89</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>14021.89</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5882.89</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5594.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 17:33:26</t>
+          <t>09/20 18:37:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -298,83 +298,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/20 12:45:32</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/20 12:18:03</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14021.89</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>14021.89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>9427</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5594.89</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4594.89</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
+++ b/bills/JXZFSP01/-1002859250998/b576905dedcb1311bf80aee31591ae37d63b79e5a37628e81fa76bdf426492c1/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 18:37:40</t>
+          <t>09/20 18:39:29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 17:33:26</t>
+          <t>09/20 18:37:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -298,12 +298,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 12:45:32</t>
+          <t>09/20 17:33:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -313,7 +313,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -325,83 +325,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/20 12:45:32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7139</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/20 12:18:03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14021.89</t>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>14021.89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14022</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4594.89</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-0.11</t>
         </is>
       </c>
     </row>
